--- a/artfynd/A 42434-2025 artfynd.xlsx
+++ b/artfynd/A 42434-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92129000</v>
+        <v>92129152</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566020.0042055835</v>
+        <v>565877</v>
       </c>
       <c r="R2" t="n">
-        <v>6506440.260884944</v>
+        <v>6506403</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-03-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-03-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>92129109</v>
       </c>
       <c r="B3" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565946.9031936593</v>
+        <v>565947</v>
       </c>
       <c r="R3" t="n">
-        <v>6506482.166629457</v>
+        <v>6506482</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2021-03-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-03-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>92129126</v>
+        <v>92129000</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565951.0594543316</v>
+        <v>566020</v>
       </c>
       <c r="R4" t="n">
-        <v>6506482.75699871</v>
+        <v>6506440</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,28 +937,17 @@
           <t>2021-03-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-03-24</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99780747</v>
+        <v>92129126</v>
       </c>
       <c r="B5" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,36 +994,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tryggerslund SSO 900 m, Ög</t>
+          <t>Övre Skriketorp, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565950.9712621083</v>
+        <v>565951</v>
       </c>
       <c r="R5" t="n">
-        <v>6506487.953887762</v>
+        <v>6506483</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,23 +1049,137 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>99780747</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tryggerslund SSO 900 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565951</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6506488</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-04-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-04-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Mirjam Ideström</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42434-2025 artfynd.xlsx
+++ b/artfynd/A 42434-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129109</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129126</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,8 +1205,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99780747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>